--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/152.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/152.xlsx
@@ -426,13 +426,13 @@
         <v>-6.047114685107984</v>
       </c>
       <c r="E2">
-        <v>-20.91046231023589</v>
+        <v>-19.64677300685296</v>
       </c>
       <c r="F2">
-        <v>-1.604923056903618</v>
+        <v>-2.436714930546297</v>
       </c>
       <c r="G2">
-        <v>-10.41291509631739</v>
+        <v>-10.72855411738299</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.97239244687442</v>
       </c>
       <c r="E3">
-        <v>-21.93696171485787</v>
+        <v>-20.1194167620411</v>
       </c>
       <c r="F3">
-        <v>-2.031175242994757</v>
+        <v>-2.237136372189812</v>
       </c>
       <c r="G3">
-        <v>-11.70288008266958</v>
+        <v>-10.7149195037559</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.895120185771615</v>
       </c>
       <c r="E4">
-        <v>-22.64275014097658</v>
+        <v>-20.26898220827083</v>
       </c>
       <c r="F4">
-        <v>-1.621355381072952</v>
+        <v>-2.356076677353376</v>
       </c>
       <c r="G4">
-        <v>-10.62063246284784</v>
+        <v>-9.908912158375268</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.837606957318065</v>
       </c>
       <c r="E5">
-        <v>-22.29432478330274</v>
+        <v>-21.29291492829406</v>
       </c>
       <c r="F5">
-        <v>-1.847194842832987</v>
+        <v>-2.265222997349132</v>
       </c>
       <c r="G5">
-        <v>-9.893030999027525</v>
+        <v>-9.997490806234854</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.80290279940014</v>
       </c>
       <c r="E6">
-        <v>-24.3674168289362</v>
+        <v>-21.93505123764844</v>
       </c>
       <c r="F6">
-        <v>-1.694636074994208</v>
+        <v>-2.42647465271289</v>
       </c>
       <c r="G6">
-        <v>-10.47376763661936</v>
+        <v>-10.0481248922072</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.804283190204572</v>
       </c>
       <c r="E7">
-        <v>-23.75690722382038</v>
+        <v>-21.99823819474439</v>
       </c>
       <c r="F7">
-        <v>-2.281664433559897</v>
+        <v>-2.342627304201524</v>
       </c>
       <c r="G7">
-        <v>-9.472272957745343</v>
+        <v>-9.897029354368815</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.837651832521453</v>
       </c>
       <c r="E8">
-        <v>-24.42199002574445</v>
+        <v>-22.67934823917097</v>
       </c>
       <c r="F8">
-        <v>-1.834968968335069</v>
+        <v>-2.220014017973946</v>
       </c>
       <c r="G8">
-        <v>-10.8321667379705</v>
+        <v>-9.629703467334066</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.901630652160659</v>
       </c>
       <c r="E9">
-        <v>-24.7993549599297</v>
+        <v>-23.00233933069156</v>
       </c>
       <c r="F9">
-        <v>-1.700916756642233</v>
+        <v>-2.044634556555443</v>
       </c>
       <c r="G9">
-        <v>-10.02972436432903</v>
+        <v>-8.943303469278403</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.983001427493112</v>
       </c>
       <c r="E10">
-        <v>-25.51761132644555</v>
+        <v>-23.6003560761423</v>
       </c>
       <c r="F10">
-        <v>-2.181599308036522</v>
+        <v>-1.975190860443955</v>
       </c>
       <c r="G10">
-        <v>-9.806958665975406</v>
+        <v>-9.122525863969146</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.066157053847232</v>
       </c>
       <c r="E11">
-        <v>-24.89179298438641</v>
+        <v>-24.91305327315821</v>
       </c>
       <c r="F11">
-        <v>-1.454011911829007</v>
+        <v>-1.854429803729038</v>
       </c>
       <c r="G11">
-        <v>-9.358514983676764</v>
+        <v>-9.060527206791685</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.139381426555768</v>
       </c>
       <c r="E12">
-        <v>-25.88602609022579</v>
+        <v>-25.0959357806357</v>
       </c>
       <c r="F12">
-        <v>-1.475130310395978</v>
+        <v>-1.796550116560631</v>
       </c>
       <c r="G12">
-        <v>-9.429387561719421</v>
+        <v>-8.388717354883457</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.188921289509214</v>
       </c>
       <c r="E13">
-        <v>-25.98541243722893</v>
+        <v>-25.78769050568782</v>
       </c>
       <c r="F13">
-        <v>-1.022535212528412</v>
+        <v>-1.840784107502722</v>
       </c>
       <c r="G13">
-        <v>-9.857340815094711</v>
+        <v>-8.553165545933092</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.21867123644927</v>
       </c>
       <c r="E14">
-        <v>-28.11777496167903</v>
+        <v>-25.75244635438532</v>
       </c>
       <c r="F14">
-        <v>-1.056611762377375</v>
+        <v>-1.607893582410057</v>
       </c>
       <c r="G14">
-        <v>-9.349339521811297</v>
+        <v>-7.98696292347999</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.226212730429881</v>
       </c>
       <c r="E15">
-        <v>-28.41715297021231</v>
+        <v>-26.55143699584452</v>
       </c>
       <c r="F15">
-        <v>-0.6344334871732044</v>
+        <v>-1.25564276988061</v>
       </c>
       <c r="G15">
-        <v>-8.949189392959067</v>
+        <v>-7.657365556458007</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.225547411081287</v>
       </c>
       <c r="E16">
-        <v>-28.97488564241787</v>
+        <v>-27.38654396298442</v>
       </c>
       <c r="F16">
-        <v>-0.5570192399119793</v>
+        <v>-1.227332485522534</v>
       </c>
       <c r="G16">
-        <v>-9.522457995648018</v>
+        <v>-7.49109376031148</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.218055633096607</v>
       </c>
       <c r="E17">
-        <v>-28.72849222736109</v>
+        <v>-27.74226235974465</v>
       </c>
       <c r="F17">
-        <v>-1.035390646252457</v>
+        <v>-0.9417022929958333</v>
       </c>
       <c r="G17">
-        <v>-8.086641151968696</v>
+        <v>-7.23097744446509</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.219988781680314</v>
       </c>
       <c r="E18">
-        <v>-30.2144634774545</v>
+        <v>-28.58869928737868</v>
       </c>
       <c r="F18">
-        <v>-0.5356713835744332</v>
+        <v>-0.6958279372316897</v>
       </c>
       <c r="G18">
-        <v>-7.75955923736025</v>
+        <v>-7.259732185391611</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.232354609337673</v>
       </c>
       <c r="E19">
-        <v>-31.30980235978551</v>
+        <v>-29.51851608556997</v>
       </c>
       <c r="F19">
-        <v>0.07946182423343762</v>
+        <v>-0.6456885150750412</v>
       </c>
       <c r="G19">
-        <v>-6.684783568558279</v>
+        <v>-6.597835330695842</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.270699979656257</v>
       </c>
       <c r="E20">
-        <v>-32.07868429574535</v>
+        <v>-29.85819893340505</v>
       </c>
       <c r="F20">
-        <v>0.4181307248265847</v>
+        <v>-0.2158420428231553</v>
       </c>
       <c r="G20">
-        <v>-7.227763617873429</v>
+        <v>-6.136495875489396</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.333347141828472</v>
       </c>
       <c r="E21">
-        <v>-31.9193857987759</v>
+        <v>-31.2839070871752</v>
       </c>
       <c r="F21">
-        <v>0.4916648991730968</v>
+        <v>-0.1621953130830537</v>
       </c>
       <c r="G21">
-        <v>-7.609065476150115</v>
+        <v>-6.595229807593911</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.430014190983356</v>
       </c>
       <c r="E22">
-        <v>-32.32073552836203</v>
+        <v>-30.47635044735856</v>
       </c>
       <c r="F22">
-        <v>0.7067430400033633</v>
+        <v>0.0379448783725292</v>
       </c>
       <c r="G22">
-        <v>-6.423683002001039</v>
+        <v>-6.401635263929087</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.554994205177716</v>
       </c>
       <c r="E23">
-        <v>-31.9468945939859</v>
+        <v>-31.00215115429318</v>
       </c>
       <c r="F23">
-        <v>1.256141980929482</v>
+        <v>0.3796919922344792</v>
       </c>
       <c r="G23">
-        <v>-7.628512912609319</v>
+        <v>-6.460836508277173</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.708031461661482</v>
       </c>
       <c r="E24">
-        <v>-32.6266776873942</v>
+        <v>-31.40506664454877</v>
       </c>
       <c r="F24">
-        <v>1.289670979925195</v>
+        <v>0.2796807105922866</v>
       </c>
       <c r="G24">
-        <v>-7.160774522410053</v>
+        <v>-6.214596299932549</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.882054535076271</v>
       </c>
       <c r="E25">
-        <v>-35.22039553865154</v>
+        <v>-31.55659448312947</v>
       </c>
       <c r="F25">
-        <v>1.204350794171651</v>
+        <v>0.4097476467102537</v>
       </c>
       <c r="G25">
-        <v>-7.216250234226619</v>
+        <v>-6.669510712700267</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.066693832701437</v>
       </c>
       <c r="E26">
-        <v>-34.83381255193084</v>
+        <v>-31.88027293112432</v>
       </c>
       <c r="F26">
-        <v>0.88709767604308</v>
+        <v>0.3840326374251486</v>
       </c>
       <c r="G26">
-        <v>-7.150146181179631</v>
+        <v>-6.499786206831992</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.25427460908621</v>
       </c>
       <c r="E27">
-        <v>-33.14874881055912</v>
+        <v>-31.71437913457104</v>
       </c>
       <c r="F27">
-        <v>0.8750697813544311</v>
+        <v>0.7569810378809448</v>
       </c>
       <c r="G27">
-        <v>-7.998754351425753</v>
+        <v>-6.733340807208395</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.425379407254739</v>
       </c>
       <c r="E28">
-        <v>-32.86708424832624</v>
+        <v>-31.53669437106656</v>
       </c>
       <c r="F28">
-        <v>1.309954384150144</v>
+        <v>0.3206882105004732</v>
       </c>
       <c r="G28">
-        <v>-6.837814973510976</v>
+        <v>-6.678956386630914</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.570016012612779</v>
       </c>
       <c r="E29">
-        <v>-33.90191084165449</v>
+        <v>-32.16651433223717</v>
       </c>
       <c r="F29">
-        <v>0.9267019215709243</v>
+        <v>0.4065534620050588</v>
       </c>
       <c r="G29">
-        <v>-7.641176329248514</v>
+        <v>-7.11574178895794</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.664130888747508</v>
       </c>
       <c r="E30">
-        <v>-32.33758925991818</v>
+        <v>-31.75774696722489</v>
       </c>
       <c r="F30">
-        <v>1.055966998042982</v>
+        <v>0.6017980021100967</v>
       </c>
       <c r="G30">
-        <v>-8.11306841409224</v>
+        <v>-7.266089348470972</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.697686726524148</v>
       </c>
       <c r="E31">
-        <v>-34.15285409971762</v>
+        <v>-31.68265275326067</v>
       </c>
       <c r="F31">
-        <v>0.7802449080211662</v>
+        <v>0.4301569627804279</v>
       </c>
       <c r="G31">
-        <v>-8.625350023132784</v>
+        <v>-7.109919828519757</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.650927465791991</v>
       </c>
       <c r="E32">
-        <v>-31.55059724597642</v>
+        <v>-31.61175951255151</v>
       </c>
       <c r="F32">
-        <v>0.7713200776234043</v>
+        <v>0.5098359665209068</v>
       </c>
       <c r="G32">
-        <v>-8.573573736401826</v>
+        <v>-7.131364484591162</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.520719143080946</v>
       </c>
       <c r="E33">
-        <v>-32.60405514530785</v>
+        <v>-31.00115853678654</v>
       </c>
       <c r="F33">
-        <v>1.5486716455541</v>
+        <v>0.2895598202380734</v>
       </c>
       <c r="G33">
-        <v>-7.891756900475862</v>
+        <v>-6.905422815442445</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.298707103192601</v>
       </c>
       <c r="E34">
-        <v>-32.0661789764463</v>
+        <v>-30.71802789095599</v>
       </c>
       <c r="F34">
-        <v>0.8487276979454069</v>
+        <v>0.337864408597521</v>
       </c>
       <c r="G34">
-        <v>-7.597236192407781</v>
+        <v>-6.878438159348698</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.992575235496099</v>
       </c>
       <c r="E35">
-        <v>-31.28860021597226</v>
+        <v>-29.98002715780191</v>
       </c>
       <c r="F35">
-        <v>0.783195552709938</v>
+        <v>0.3960257406828799</v>
       </c>
       <c r="G35">
-        <v>-7.039790007313273</v>
+        <v>-7.180932081398039</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.608521693132685</v>
       </c>
       <c r="E36">
-        <v>-31.70062162205754</v>
+        <v>-29.47308410688768</v>
       </c>
       <c r="F36">
-        <v>0.8929194421499549</v>
+        <v>0.1875082696827855</v>
       </c>
       <c r="G36">
-        <v>-7.824391857791366</v>
+        <v>-6.920925416824476</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.164056813829779</v>
       </c>
       <c r="E37">
-        <v>-29.55313933177941</v>
+        <v>-29.89285332869942</v>
       </c>
       <c r="F37">
-        <v>-0.05419359947345701</v>
+        <v>0.2066418999526485</v>
       </c>
       <c r="G37">
-        <v>-7.70562386485244</v>
+        <v>-6.6135650668573</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.677717760838321</v>
       </c>
       <c r="E38">
-        <v>-31.17080475977181</v>
+        <v>-28.94050120585961</v>
       </c>
       <c r="F38">
-        <v>0.5156229411968641</v>
+        <v>0.06955786356556673</v>
       </c>
       <c r="G38">
-        <v>-7.043575586970387</v>
+        <v>-6.674536396038159</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.170708259957461</v>
       </c>
       <c r="E39">
-        <v>-30.32355795592944</v>
+        <v>-28.33935501567562</v>
       </c>
       <c r="F39">
-        <v>-0.01559085013559725</v>
+        <v>-0.1865244637032752</v>
       </c>
       <c r="G39">
-        <v>-7.655252158711501</v>
+        <v>-6.010548334924908</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.669223212545128</v>
       </c>
       <c r="E40">
-        <v>-29.03288939178042</v>
+        <v>-28.37503317756155</v>
       </c>
       <c r="F40">
-        <v>-0.07647751097616651</v>
+        <v>0.02517393812356922</v>
       </c>
       <c r="G40">
-        <v>-7.211261101313002</v>
+        <v>-6.165255837905099</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.191981858335874</v>
       </c>
       <c r="E41">
-        <v>-30.7177454725859</v>
+        <v>-27.5128846514857</v>
       </c>
       <c r="F41">
-        <v>0.5028271499258201</v>
+        <v>-0.03582869415339197</v>
       </c>
       <c r="G41">
-        <v>-6.380073124351083</v>
+        <v>-6.35375420812807</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.766200856987751</v>
       </c>
       <c r="E42">
-        <v>-29.53986359177959</v>
+        <v>-27.36682036240281</v>
       </c>
       <c r="F42">
-        <v>0.2302362886865868</v>
+        <v>-0.1920513310147535</v>
       </c>
       <c r="G42">
-        <v>-6.638763973650725</v>
+        <v>-6.274745244567209</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.403685604995795</v>
       </c>
       <c r="E43">
-        <v>-30.1142298753411</v>
+        <v>-26.23600890214644</v>
       </c>
       <c r="F43">
-        <v>0.1410757916536649</v>
+        <v>-0.02150870686119691</v>
       </c>
       <c r="G43">
-        <v>-7.632617003106549</v>
+        <v>-6.177001577820518</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.125617355182549</v>
       </c>
       <c r="E44">
-        <v>-29.93769970458492</v>
+        <v>-26.89971283791066</v>
       </c>
       <c r="F44">
-        <v>0.5689797423459859</v>
+        <v>-0.1345129312162999</v>
       </c>
       <c r="G44">
-        <v>-6.24416820391609</v>
+        <v>-5.819125930759891</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.933870398302585</v>
       </c>
       <c r="E45">
-        <v>-28.86505396893278</v>
+        <v>-26.64475550110209</v>
       </c>
       <c r="F45">
-        <v>-0.1761847817815318</v>
+        <v>-0.0686229312628216</v>
       </c>
       <c r="G45">
-        <v>-5.967802613734611</v>
+        <v>-5.816583065528147</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.83860044859344</v>
       </c>
       <c r="E46">
-        <v>-27.22097619352013</v>
+        <v>-26.13318369616633</v>
       </c>
       <c r="F46">
-        <v>0.7633544966780843</v>
+        <v>-0.234819940021292</v>
       </c>
       <c r="G46">
-        <v>-6.560185782947397</v>
+        <v>-5.83994661887402</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.830907183117818</v>
       </c>
       <c r="E47">
-        <v>-25.13182367969355</v>
+        <v>-25.30580170209062</v>
       </c>
       <c r="F47">
-        <v>0.05764759704811544</v>
+        <v>0.1315371410104285</v>
       </c>
       <c r="G47">
-        <v>-5.773179436700889</v>
+        <v>-5.953842962405928</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.909995872291999</v>
       </c>
       <c r="E48">
-        <v>-26.25908414426718</v>
+        <v>-25.01426703314428</v>
       </c>
       <c r="F48">
-        <v>-0.03000361457690584</v>
+        <v>-0.2782810641765709</v>
       </c>
       <c r="G48">
-        <v>-5.973577580770153</v>
+        <v>-5.532233818387043</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.059107670128301</v>
       </c>
       <c r="E49">
-        <v>-24.28613848330931</v>
+        <v>-24.63315174913271</v>
       </c>
       <c r="F49">
-        <v>0.4957346682230508</v>
+        <v>0.008985153970658485</v>
       </c>
       <c r="G49">
-        <v>-5.241670999119091</v>
+        <v>-5.707957815325696</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.27068926604628</v>
       </c>
       <c r="E50">
-        <v>-26.02921220386057</v>
+        <v>-24.05079261037658</v>
       </c>
       <c r="F50">
-        <v>-0.2467915057265505</v>
+        <v>-0.1919809197855156</v>
       </c>
       <c r="G50">
-        <v>-5.722468333763104</v>
+        <v>-5.999089776914512</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.525061013621513</v>
       </c>
       <c r="E51">
-        <v>-26.66477397968776</v>
+        <v>-23.34256624921019</v>
       </c>
       <c r="F51">
-        <v>0.2460084040358894</v>
+        <v>-0.4366350903653355</v>
       </c>
       <c r="G51">
-        <v>-5.875251717979645</v>
+        <v>-5.738521802253859</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.811876451057499</v>
       </c>
       <c r="E52">
-        <v>-25.67202357029134</v>
+        <v>-24.09878296723497</v>
       </c>
       <c r="F52">
-        <v>0.09683600213975445</v>
+        <v>-0.1467562014296766</v>
       </c>
       <c r="G52">
-        <v>-6.303896818671579</v>
+        <v>-5.741252641096164</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.115331869907243</v>
       </c>
       <c r="E53">
-        <v>-24.24650438763647</v>
+        <v>-23.02512800123089</v>
       </c>
       <c r="F53">
-        <v>0.2397194387138356</v>
+        <v>-0.3126301469010552</v>
       </c>
       <c r="G53">
-        <v>-5.820071020301874</v>
+        <v>-5.690181255404806</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.425199791814449</v>
       </c>
       <c r="E54">
-        <v>-23.54277595433487</v>
+        <v>-23.01142655707028</v>
       </c>
       <c r="F54">
-        <v>0.5139653780238623</v>
+        <v>-0.3595637872088696</v>
       </c>
       <c r="G54">
-        <v>-5.948634526946657</v>
+        <v>-5.986717458297226</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.732135697469867</v>
       </c>
       <c r="E55">
-        <v>-25.36845289492565</v>
+        <v>-22.47035033888294</v>
       </c>
       <c r="F55">
-        <v>0.1704869762900613</v>
+        <v>-0.3236739411151782</v>
       </c>
       <c r="G55">
-        <v>-6.270899617784498</v>
+        <v>-6.119873264677778</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.025439872262392</v>
       </c>
       <c r="E56">
-        <v>-23.90908503997343</v>
+        <v>-22.20436207279563</v>
       </c>
       <c r="F56">
-        <v>0.3535959339440864</v>
+        <v>-0.516154219197074</v>
       </c>
       <c r="G56">
-        <v>-5.849763018536605</v>
+        <v>-6.397259655994382</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.299731931829884</v>
       </c>
       <c r="E57">
-        <v>-22.93990825805674</v>
+        <v>-21.39245494411622</v>
       </c>
       <c r="F57">
-        <v>-0.4098655693764667</v>
+        <v>-0.4402533991807638</v>
       </c>
       <c r="G57">
-        <v>-6.366189184615543</v>
+        <v>-6.6411214760165</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.544449440270372</v>
       </c>
       <c r="E58">
-        <v>-24.0084921530332</v>
+        <v>-21.48237612251008</v>
       </c>
       <c r="F58">
-        <v>-0.111234978830231</v>
+        <v>-0.3205278017193456</v>
       </c>
       <c r="G58">
-        <v>-6.084359306004863</v>
+        <v>-6.662767159421421</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.758251449723442</v>
       </c>
       <c r="E59">
-        <v>-22.70697540090373</v>
+        <v>-21.41380660353716</v>
       </c>
       <c r="F59">
-        <v>0.4445109131361378</v>
+        <v>-0.3988226035297465</v>
       </c>
       <c r="G59">
-        <v>-7.616254161381746</v>
+        <v>-6.730119148382961</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.932015714276197</v>
       </c>
       <c r="E60">
-        <v>-23.43418193782458</v>
+        <v>-21.14817551362378</v>
       </c>
       <c r="F60">
-        <v>0.1949196728356327</v>
+        <v>-0.4382313543505302</v>
       </c>
       <c r="G60">
-        <v>-6.334322436136413</v>
+        <v>-6.536798732900205</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.066690762700802</v>
       </c>
       <c r="E61">
-        <v>-22.98357927513731</v>
+        <v>-21.13217734360054</v>
       </c>
       <c r="F61">
-        <v>0.6025667270598947</v>
+        <v>-0.5905258729878166</v>
       </c>
       <c r="G61">
-        <v>-7.591795400679901</v>
+        <v>-6.780939902593572</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.154096931757613</v>
       </c>
       <c r="E62">
-        <v>-23.12083044978892</v>
+        <v>-20.560437966202</v>
       </c>
       <c r="F62">
-        <v>0.05920658450018411</v>
+        <v>-0.710567906797104</v>
       </c>
       <c r="G62">
-        <v>-7.250949640587106</v>
+        <v>-7.38978642719792</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.196804370276451</v>
       </c>
       <c r="E63">
-        <v>-22.75628647896342</v>
+        <v>-20.52371111845654</v>
       </c>
       <c r="F63">
-        <v>-0.2267251337611352</v>
+        <v>-0.7268519532013368</v>
       </c>
       <c r="G63">
-        <v>-7.343555361978486</v>
+        <v>-7.149877274486746</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.188915645906293</v>
       </c>
       <c r="E64">
-        <v>-22.61521019668164</v>
+        <v>-20.35170587143876</v>
       </c>
       <c r="F64">
-        <v>0.05262851895455324</v>
+        <v>-0.6547359438484174</v>
       </c>
       <c r="G64">
-        <v>-7.592596899269373</v>
+        <v>-7.630517964455294</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.133951001053385</v>
       </c>
       <c r="E65">
-        <v>-21.28923102984893</v>
+        <v>-20.52979141983608</v>
       </c>
       <c r="F65">
-        <v>0.03470679019498593</v>
+        <v>-0.8185340006083804</v>
       </c>
       <c r="G65">
-        <v>-8.186718824379842</v>
+        <v>-7.486678991207907</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.029819861644363</v>
       </c>
       <c r="E66">
-        <v>-21.54889395508854</v>
+        <v>-20.57411864430598</v>
       </c>
       <c r="F66">
-        <v>-0.3852456617978626</v>
+        <v>-0.9251341165724404</v>
       </c>
       <c r="G66">
-        <v>-6.981612174844904</v>
+        <v>-7.770600076236068</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.879505611419583</v>
       </c>
       <c r="E67">
-        <v>-21.8695883207465</v>
+        <v>-20.14089717101312</v>
       </c>
       <c r="F67">
-        <v>0.3896183188222257</v>
+        <v>-0.7918845928929176</v>
       </c>
       <c r="G67">
-        <v>-9.374702905513962</v>
+        <v>-7.79056182937972</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.685819260179916</v>
       </c>
       <c r="E68">
-        <v>-21.65233383634472</v>
+        <v>-19.97311989312401</v>
       </c>
       <c r="F68">
-        <v>-0.46071655913212</v>
+        <v>-0.7231524643804341</v>
       </c>
       <c r="G68">
-        <v>-7.892989171922868</v>
+        <v>-7.651852969253871</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.450652960423725</v>
       </c>
       <c r="E69">
-        <v>-21.62561207468077</v>
+        <v>-20.45174842583123</v>
       </c>
       <c r="F69">
-        <v>-0.1668275435995086</v>
+        <v>-1.103877578013712</v>
       </c>
       <c r="G69">
-        <v>-8.505169617370067</v>
+        <v>-8.029991910458424</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.182727740036296</v>
       </c>
       <c r="E70">
-        <v>-22.2825587356195</v>
+        <v>-20.56652657400419</v>
       </c>
       <c r="F70">
-        <v>-0.4186528907853639</v>
+        <v>-0.9440855060136875</v>
       </c>
       <c r="G70">
-        <v>-8.881298285239462</v>
+        <v>-7.484047360660065</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.88412957843494</v>
       </c>
       <c r="E71">
-        <v>-21.61253776543021</v>
+        <v>-20.14073934898277</v>
       </c>
       <c r="F71">
-        <v>-0.6532216882360999</v>
+        <v>-1.152359436997359</v>
       </c>
       <c r="G71">
-        <v>-8.55171788805732</v>
+        <v>-7.648178346241879</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.56838977423969</v>
       </c>
       <c r="E72">
-        <v>-23.06347044818171</v>
+        <v>-19.82196792016821</v>
       </c>
       <c r="F72">
-        <v>-0.4899388760006781</v>
+        <v>-1.149574465789147</v>
       </c>
       <c r="G72">
-        <v>-8.278956430783873</v>
+        <v>-7.89267979868882</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.238827648405707</v>
       </c>
       <c r="E73">
-        <v>-21.49976561832714</v>
+        <v>-20.58201389903448</v>
       </c>
       <c r="F73">
-        <v>-0.2017564835059525</v>
+        <v>-1.129817903232379</v>
       </c>
       <c r="G73">
-        <v>-7.564403468429941</v>
+        <v>-7.782408474021673</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.909221879824924</v>
       </c>
       <c r="E74">
-        <v>-22.46097238771148</v>
+        <v>-20.76279903479294</v>
       </c>
       <c r="F74">
-        <v>-0.5563076723129745</v>
+        <v>-1.353869748137172</v>
       </c>
       <c r="G74">
-        <v>-8.480742185603315</v>
+        <v>-8.146463753529465</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.583067573023424</v>
       </c>
       <c r="E75">
-        <v>-21.87801103331325</v>
+        <v>-19.72182153549262</v>
       </c>
       <c r="F75">
-        <v>-0.5713466825107996</v>
+        <v>-1.482304800471624</v>
       </c>
       <c r="G75">
-        <v>-8.117920482914824</v>
+        <v>-7.521433223204807</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.271461237620987</v>
       </c>
       <c r="E76">
-        <v>-24.23449330048507</v>
+        <v>-20.752839634036</v>
       </c>
       <c r="F76">
-        <v>-1.120877333853963</v>
+        <v>-1.48135963326503</v>
       </c>
       <c r="G76">
-        <v>-8.695064735949282</v>
+        <v>-7.314521271380714</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.975953830497675</v>
       </c>
       <c r="E77">
-        <v>-23.37438815438102</v>
+        <v>-21.43612596119679</v>
       </c>
       <c r="F77">
-        <v>-1.2055149448676</v>
+        <v>-1.597234979038236</v>
       </c>
       <c r="G77">
-        <v>-8.509404245096851</v>
+        <v>-7.234601157957555</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.701943356760622</v>
       </c>
       <c r="E78">
-        <v>-24.45042706368555</v>
+        <v>-22.06945330933122</v>
       </c>
       <c r="F78">
-        <v>-0.5460094087613711</v>
+        <v>-1.688833361337597</v>
       </c>
       <c r="G78">
-        <v>-7.585845513756754</v>
+        <v>-6.771439403026511</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.448760846443125</v>
       </c>
       <c r="E79">
-        <v>-23.85747308283978</v>
+        <v>-22.48514407762199</v>
       </c>
       <c r="F79">
-        <v>-1.226088277683529</v>
+        <v>-1.724856574583139</v>
       </c>
       <c r="G79">
-        <v>-7.357723872874457</v>
+        <v>-7.279680884812308</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.216533864739183</v>
       </c>
       <c r="E80">
-        <v>-23.7923714953231</v>
+        <v>-22.3310184053576</v>
       </c>
       <c r="F80">
-        <v>-1.060086763632119</v>
+        <v>-1.872869262115355</v>
       </c>
       <c r="G80">
-        <v>-6.983656387859746</v>
+        <v>-6.663955048210378</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.003759868211788</v>
       </c>
       <c r="E81">
-        <v>-23.57258770522449</v>
+        <v>-22.79083704397467</v>
       </c>
       <c r="F81">
-        <v>-1.48706459956811</v>
+        <v>-1.852999213224403</v>
       </c>
       <c r="G81">
-        <v>-7.530051291100072</v>
+        <v>-6.436963859736032</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.805838819528396</v>
       </c>
       <c r="E82">
-        <v>-24.50711839826946</v>
+        <v>-23.56793195532936</v>
       </c>
       <c r="F82">
-        <v>-2.005738565156993</v>
+        <v>-1.819684761386015</v>
       </c>
       <c r="G82">
-        <v>-7.021399922413471</v>
+        <v>-5.79414893725671</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.620361864609322</v>
       </c>
       <c r="E83">
-        <v>-25.71032033191759</v>
+        <v>-24.2645750101108</v>
       </c>
       <c r="F83">
-        <v>-1.219670915414041</v>
+        <v>-2.069826866009382</v>
       </c>
       <c r="G83">
-        <v>-6.670189506293956</v>
+        <v>-6.158869956635236</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.438957118893086</v>
       </c>
       <c r="E84">
-        <v>-25.15728286511474</v>
+        <v>-24.67416471096539</v>
       </c>
       <c r="F84">
-        <v>-1.582461046409307</v>
+        <v>-1.82370151492219</v>
       </c>
       <c r="G84">
-        <v>-6.946077330215261</v>
+        <v>-6.144696224250082</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.258549315268428</v>
       </c>
       <c r="E85">
-        <v>-27.62540345269795</v>
+        <v>-25.54567872857874</v>
       </c>
       <c r="F85">
-        <v>-1.245983177596565</v>
+        <v>-1.988805078708965</v>
       </c>
       <c r="G85">
-        <v>-6.752939666853883</v>
+        <v>-5.866336025200993</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.070897653376408</v>
       </c>
       <c r="E86">
-        <v>-28.34419350686904</v>
+        <v>-26.48781810477079</v>
       </c>
       <c r="F86">
-        <v>-1.831484026671492</v>
+        <v>-2.019085220750898</v>
       </c>
       <c r="G86">
-        <v>-6.955593494249869</v>
+        <v>-5.661254205335271</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.8762663972005755</v>
       </c>
       <c r="E87">
-        <v>-28.99245164971623</v>
+        <v>-27.7246901226293</v>
       </c>
       <c r="F87">
-        <v>-2.039632045809937</v>
+        <v>-2.218698570538301</v>
       </c>
       <c r="G87">
-        <v>-6.706826085141048</v>
+        <v>-5.546444101196473</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.6732125677682941</v>
       </c>
       <c r="E88">
-        <v>-30.28935210745815</v>
+        <v>-28.68074068015387</v>
       </c>
       <c r="F88">
-        <v>-2.139993726863514</v>
+        <v>-2.286463994291717</v>
       </c>
       <c r="G88">
-        <v>-7.204676803454214</v>
+        <v>-5.545177890069783</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.4677760432052148</v>
       </c>
       <c r="E89">
-        <v>-31.13727380814081</v>
+        <v>-29.46654279905107</v>
       </c>
       <c r="F89">
-        <v>-1.429477326092891</v>
+        <v>-2.348644565015459</v>
       </c>
       <c r="G89">
-        <v>-6.602438073409974</v>
+        <v>-5.583790802572349</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.2653537781906882</v>
       </c>
       <c r="E90">
-        <v>-31.53635173113226</v>
+        <v>-30.85037204642732</v>
       </c>
       <c r="F90">
-        <v>-2.305647326605748</v>
+        <v>-2.632198040463341</v>
       </c>
       <c r="G90">
-        <v>-6.726448441487856</v>
+        <v>-5.530291424411255</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.07572000424874759</v>
       </c>
       <c r="E91">
-        <v>-33.49104610492318</v>
+        <v>-32.20752521746419</v>
       </c>
       <c r="F91">
-        <v>-2.079935433425744</v>
+        <v>-2.454239871319924</v>
       </c>
       <c r="G91">
-        <v>-6.567822210876404</v>
+        <v>-5.23395624885235</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.09251220078746236</v>
       </c>
       <c r="E92">
-        <v>-35.29887461984551</v>
+        <v>-33.31576605077577</v>
       </c>
       <c r="F92">
-        <v>-1.648008102258026</v>
+        <v>-2.649023010781602</v>
       </c>
       <c r="G92">
-        <v>-7.357029414813221</v>
+        <v>-5.438471537141801</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.2284797305109</v>
       </c>
       <c r="E93">
-        <v>-35.71611661256609</v>
+        <v>-34.55605616155462</v>
       </c>
       <c r="F93">
-        <v>-2.088446080122107</v>
+        <v>-2.712286257700803</v>
       </c>
       <c r="G93">
-        <v>-6.590478252438085</v>
+        <v>-5.928926016028343</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.3238341582662679</v>
       </c>
       <c r="E94">
-        <v>-37.71771735505962</v>
+        <v>-36.67781761409809</v>
       </c>
       <c r="F94">
-        <v>-1.486091267869821</v>
+        <v>-2.733707838737198</v>
       </c>
       <c r="G94">
-        <v>-7.535591291122414</v>
+        <v>-6.029011520673262</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.3723425379180912</v>
       </c>
       <c r="E95">
-        <v>-39.97047939921083</v>
+        <v>-38.44146634355256</v>
       </c>
       <c r="F95">
-        <v>-2.117133271648456</v>
+        <v>-3.06434737409501</v>
       </c>
       <c r="G95">
-        <v>-7.441701083392207</v>
+        <v>-6.258806648838462</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.3672205487530957</v>
       </c>
       <c r="E96">
-        <v>-42.84168160550263</v>
+        <v>-39.33032624826405</v>
       </c>
       <c r="F96">
-        <v>-2.620262922923806</v>
+        <v>-2.825307877771365</v>
       </c>
       <c r="G96">
-        <v>-8.254497670082028</v>
+        <v>-6.490014189827455</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.3103903942620977</v>
       </c>
       <c r="E97">
-        <v>-42.92673106701246</v>
+        <v>-42.08223784227845</v>
       </c>
       <c r="F97">
-        <v>-2.695500220650474</v>
+        <v>-2.804239181248562</v>
       </c>
       <c r="G97">
-        <v>-7.574734184776975</v>
+        <v>-6.892021863456261</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.195146692682061</v>
       </c>
       <c r="E98">
-        <v>-44.00454547415836</v>
+        <v>-43.26307057973106</v>
       </c>
       <c r="F98">
-        <v>-2.802977577694099</v>
+        <v>-3.095909828876477</v>
       </c>
       <c r="G98">
-        <v>-7.917893064577497</v>
+        <v>-7.043121317411533</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.03706649087818134</v>
       </c>
       <c r="E99">
-        <v>-45.20705174490958</v>
+        <v>-45.06693277783818</v>
       </c>
       <c r="F99">
-        <v>-3.346368369847712</v>
+        <v>-3.251277590578149</v>
       </c>
       <c r="G99">
-        <v>-8.429951454955502</v>
+        <v>-7.385768491272196</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.1744710151290942</v>
       </c>
       <c r="E100">
-        <v>-49.01497338661452</v>
+        <v>-47.2286086678189</v>
       </c>
       <c r="F100">
-        <v>-2.898735192722916</v>
+        <v>-3.214522100548532</v>
       </c>
       <c r="G100">
-        <v>-8.300629527007001</v>
+        <v>-7.472878595299282</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.4010880069526803</v>
       </c>
       <c r="E101">
-        <v>-49.45087056630341</v>
+        <v>-49.42424017528861</v>
       </c>
       <c r="F101">
-        <v>-3.218416255709093</v>
+        <v>-3.263727952642225</v>
       </c>
       <c r="G101">
-        <v>-9.02944629243448</v>
+        <v>-7.904264977811886</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.6771254001872528</v>
       </c>
       <c r="E102">
-        <v>-52.11544531767083</v>
+        <v>-51.26222515764051</v>
       </c>
       <c r="F102">
-        <v>-2.908562115222326</v>
+        <v>-3.307077247198126</v>
       </c>
       <c r="G102">
-        <v>-8.556422449810507</v>
+        <v>-8.219849173241069</v>
       </c>
     </row>
   </sheetData>
